--- a/呉俊鋒_週報_2025年5月分.xlsx
+++ b/呉俊鋒_週報_2025年5月分.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CD2A35-4C5A-4472-8879-688FE75F416E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA75E258-546B-4BF9-9A96-7881035FAD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年5月12日の週" sheetId="6" r:id="rId1"/>
     <sheet name="2025年5月19日の週" sheetId="7" r:id="rId2"/>
+    <sheet name="2025年5月26日の週" sheetId="8" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="Holiday">[1]祝日!$A$2:$B$335</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2025年5月12日の週'!$A$1:$K$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2025年5月19日の週'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2025年5月26日の週'!$A$1:$K$20</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -325,12 +327,180 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>・5/26
+　Spring AOPとはなんですか？プロキシメカニズムとは？
+・5/27　
+　Spring AOPについて、中国語のドキュメントと日本語のドキュメント記述が違う</t>
+    <rPh sb="61" eb="64">
+      <t>チュウゴクゴ</t>
+    </rPh>
+    <rPh sb="72" eb="75">
+      <t>ニホンゴ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・5/26
+　Spring AOPとはなんですか？プロキシメカニズムとは？
+　　</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>成果物参照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・5/27　
+　Spring AOPについて、中国語のドキュメントと日本語のドキュメント記述が違う
+　　釘宮さんと一緒に英語版のドキュメントを見て、日本語版のドキュメントの翻訳は間違えた</t>
+    </r>
+    <rPh sb="40" eb="43">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>クギミヤ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="120" eb="123">
+      <t>ニホンゴ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>ホンヤク</t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t>マチガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今週の進捗状況：Springフレームワーク復習、Django引き続き勉強する
+来週の進捗予定：Djangoのプロジェット例着手、時間があればAngular或はReactの勉強を着手する</t>
+    <rPh sb="60" eb="61">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>チャクシュ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>アルイ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>チャクシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・5/26
+　SpringのIOC、DI、MVCを復習した　
+　Spring AOP API復習した
+・5/27～5/28
+　長い時間で見なかったので、Djangoの知識を復習した
+・5/29
+　DjangoのORM機能を利用して、結合検索した内容を画面に表示できた
+　ORM利用しなくても、SQL文利用しても結合検索した内容を画面に表示できた
+・5/30
+　魏さんにFlaskの勉強をサポートした
+　DjangoのFormクラスを勉強した</t>
+    <rPh sb="25" eb="27">
+      <t>フクシュウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>フクシュウ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="116" eb="120">
+      <t>ケツゴウケンサク</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="138" eb="140">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="149" eb="150">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="180" eb="181">
+      <t>ギ</t>
+    </rPh>
+    <rPh sb="190" eb="192">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="216" eb="218">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,6 +548,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -677,7 +856,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -770,6 +949,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4342,4 +4542,308 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9763235-1E93-42A2-9569-E077D1BC81FB}">
+  <dimension ref="B1:M20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="7.8984375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="16.3984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.09765625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" s="2" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="25"/>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
+    </row>
+    <row r="3" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B4" s="13"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B5" s="13"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B6" s="13"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B7" s="13"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+    </row>
+    <row r="8" spans="2:13" ht="364.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="26"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="37"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B10" s="13"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B12" s="13"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="2:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="30"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B16" s="13"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B17" s="13"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B18" s="13"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B19" s="13"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="2:11" ht="147.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="14"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C15:K20"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:K8"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:K14"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>